--- a/Config/Datas/Tables/s_属性_AttributeConfig.xlsx
+++ b/Config/Datas/Tables/s_属性_AttributeConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbAttribute" sheetId="1" r:id="Rc8545082b60e48e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbAttribute" sheetId="1" r:id="R3b9db34319c94c17"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -564,15 +564,11 @@
       <x:c r="G1" s="38" t="str">
         <x:v>unit</x:v>
       </x:c>
-      <x:c r="H1" s="38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">minValueMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" s="38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">maxValueMilli</x:t>
-        </x:is>
+      <x:c r="H1" s="38" t="str">
+        <x:v>minValueMilli</x:v>
+      </x:c>
+      <x:c r="I1" s="38" t="str">
+        <x:v>maxValueMilli</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
@@ -597,15 +593,11 @@
       <x:c r="G2" s="40" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="H2" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">long</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" s="40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">long</x:t>
-        </x:is>
+      <x:c r="H2" s="40" t="str">
+        <x:v>long</x:v>
+      </x:c>
+      <x:c r="I2" s="40" t="str">
+        <x:v>long</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -643,15 +635,11 @@
       <x:c r="G4" s="42" t="str">
         <x:v>属性单位</x:v>
       </x:c>
-      <x:c r="H4" s="42" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">合法下限；调试值；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" s="42" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">合法上限；调试值；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
+      <x:c r="H4" s="42" t="str">
+        <x:v>合法下限；调试值；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="I4" s="42" t="str">
+        <x:v>合法上限；调试值；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
@@ -1032,6 +1020,33 @@
         <x:v>1000000</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>技能范围</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>0.###</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>SkillRangeMultiplier</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>倍率</x:v>
+      </x:c>
+      <x:c r="H19" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I19" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
